--- a/Statistical_documentation_in_R/main_results/panel_wb.xlsx
+++ b/Statistical_documentation_in_R/main_results/panel_wb.xlsx
@@ -65,7 +65,7 @@
     <t xml:space="preserve">GDPpc</t>
   </si>
   <si>
-    <t xml:space="preserve">Pop15_65</t>
+    <t xml:space="preserve">Pop15_64</t>
   </si>
   <si>
     <t xml:space="preserve">YouthUnempl</t>
@@ -7359,7 +7359,7 @@
         <v>30</v>
       </c>
       <c r="G95" t="n">
-        <v>8.43598313599069</v>
+        <v>8.4359831359907</v>
       </c>
       <c r="H95" t="n">
         <v>1</v>
@@ -19374,7 +19374,7 @@
         <v>117</v>
       </c>
       <c r="N290" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -19434,7 +19434,7 @@
         <v>117</v>
       </c>
       <c r="N291" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -19496,7 +19496,7 @@
         <v>117</v>
       </c>
       <c r="N292" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O292" t="n">
         <v>0</v>
@@ -19556,7 +19556,7 @@
         <v>117</v>
       </c>
       <c r="N293" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O293" t="n">
         <v>0</v>
@@ -19618,7 +19618,7 @@
         <v>117</v>
       </c>
       <c r="N294" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O294" t="n">
         <v>0</v>
@@ -19680,7 +19680,7 @@
         <v>117</v>
       </c>
       <c r="N295" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O295" t="n">
         <v>0</v>
@@ -19740,7 +19740,7 @@
         <v>117</v>
       </c>
       <c r="N296" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -19800,7 +19800,7 @@
         <v>117</v>
       </c>
       <c r="N297" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -19860,7 +19860,7 @@
         <v>117</v>
       </c>
       <c r="N298" t="n">
-        <v>0.999999991097277</v>
+        <v>0.999999991097276</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -20079,7 +20079,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>6.32793678372919</v>
+        <v>6.3279367837292</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -29777,7 +29777,7 @@
         <v>397</v>
       </c>
       <c r="Q460" t="n">
-        <v>11402.509661649</v>
+        <v>10469.2210966932</v>
       </c>
       <c r="R460" t="n">
         <v>3696945</v>
